--- a/datasets/precaution_dataset.xlsx
+++ b/datasets/precaution_dataset.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DriveD\fyp\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B167F976-ABE4-42EE-A5D6-CB0D29C779F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8E968D-4891-400F-AF80-965428FC1608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6828" yWindow="396" windowWidth="14040" windowHeight="11844"/>
+    <workbookView xWindow="4548" yWindow="396" windowWidth="18432" windowHeight="11844" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="precaution_dataset" sheetId="1" r:id="rId1"/>
@@ -358,9 +358,6 @@
     <t>Reframe feedback through positive affirmations and cognitive restructuring.</t>
   </si>
   <si>
-    <t>Dissocative Identity Disorder (DID)</t>
-  </si>
-  <si>
     <t>Establish a daily routine and seek regular therapy for identity integration.</t>
   </si>
   <si>
@@ -424,9 +421,6 @@
     <t>Avoid spicy/greasy foods and practice mindful breathing during meals.</t>
   </si>
   <si>
-    <t>Substance use disorder</t>
-  </si>
-  <si>
     <t>Distract yourself with engaging activities like hobbies, exercise, or calling a support person.</t>
   </si>
   <si>
@@ -457,9 +451,6 @@
     <t>Engage in integrated care—address both mental and physical symptoms through therapy and regular checkups.</t>
   </si>
   <si>
-    <t>Attention Defict Hyperactivity Disorder (ADHD)</t>
-  </si>
-  <si>
     <t>Break tasks into short, timed intervals (e.g., Pomodoro technique).</t>
   </si>
   <si>
@@ -523,9 +514,6 @@
     <t>Engage in goal-setting and talk to a therapist about emotions.</t>
   </si>
   <si>
-    <t>insomnia</t>
-  </si>
-  <si>
     <t>Create a relaxing pre-sleep routine with no screens or stimulants.</t>
   </si>
   <si>
@@ -655,9 +643,6 @@
     <t>Reconnect slowly with supportive people through short conversations or walks.</t>
   </si>
   <si>
-    <t>Sepration Anxiety Disorder</t>
-  </si>
-  <si>
     <t>Practice short periods of separation with reassurance and comfort items.</t>
   </si>
   <si>
@@ -688,9 +673,6 @@
     <t>Gradually build confidence with timed, positive reinforcement.</t>
   </si>
   <si>
-    <t>Dissocative Amnesia</t>
-  </si>
-  <si>
     <t>Use memory aids like notebooks or digital reminders for important details.</t>
   </si>
   <si>
@@ -719,12 +701,30 @@
   </si>
   <si>
     <t>Break tasks into steps and repeat instructions when needed.</t>
+  </si>
+  <si>
+    <t>ADHD (Attention Deficit Hyperactivity Disorder)</t>
+  </si>
+  <si>
+    <t>Dissociative Identity Disorder</t>
+  </si>
+  <si>
+    <t>Substance Use Disorder</t>
+  </si>
+  <si>
+    <t>Insomnia</t>
+  </si>
+  <si>
+    <t>Separation Anxiety Disorder</t>
+  </si>
+  <si>
+    <t>Dissociative Amnesia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1558,10 +1558,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B211"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="35.33203125" customWidth="1"/>
     <col min="2" max="2" width="68.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2375,882 +2376,882 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" t="s">
         <v>112</v>
-      </c>
-      <c r="B102" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B108" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" t="s">
         <v>123</v>
-      </c>
-      <c r="B112" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B122" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>229</v>
+      </c>
+      <c r="B123" t="s">
         <v>134</v>
-      </c>
-      <c r="B123" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B126" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B128" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B129" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B130" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B133" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>227</v>
+      </c>
+      <c r="B134" t="s">
         <v>145</v>
-      </c>
-      <c r="B134" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B135" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B136" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B137" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B140" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B141" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B142" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" t="s">
         <v>156</v>
-      </c>
-      <c r="B144" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B147" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B149" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B150" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B151" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B152" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B153" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B154" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>230</v>
+      </c>
+      <c r="B155" t="s">
         <v>167</v>
-      </c>
-      <c r="B155" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B156" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B157" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B158" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B159" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B160" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="B161" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B162" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B163" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B164" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" t="s">
         <v>178</v>
-      </c>
-      <c r="B165" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B166" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B168" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B170" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B171" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B172" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B173" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B174" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" t="s">
         <v>189</v>
-      </c>
-      <c r="B175" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B176" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B177" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B178" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B179" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B181" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B182" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B183" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B184" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>196</v>
+      </c>
+      <c r="B185" t="s">
         <v>200</v>
-      </c>
-      <c r="B185" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B186" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B187" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B188" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B189" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B190" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B192" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B193" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B194" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B195" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
+        <v>231</v>
+      </c>
+      <c r="B196" t="s">
         <v>211</v>
-      </c>
-      <c r="B196" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B197" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B199" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B200" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B201" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B202" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B203" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B204" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B205" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B206" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>232</v>
+      </c>
+      <c r="B207" t="s">
         <v>222</v>
-      </c>
-      <c r="B207" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B208" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B209" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B210" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B211" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
